--- a/GRAMMAR/4_21_12.xlsx
+++ b/GRAMMAR/4_21_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0CBDD3-B13E-4C18-B57B-7F29A8F27F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FCF07A-5748-4AB4-B8E5-1B824ED7B107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10560" yWindow="960" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Fre</t>
   </si>
@@ -81,209 +81,323 @@
     <t>Ｖる+つもり-&gt;准备做某事</t>
   </si>
   <si>
+    <t>多么...啊</t>
+  </si>
+  <si>
+    <t>なんて～だろう-&gt;(感叹)多么…的啊</t>
+  </si>
+  <si>
+    <t>どうしても</t>
+  </si>
+  <si>
+    <t>(1)接否定，无论…也不…(2)务必</t>
+  </si>
+  <si>
+    <t>どんなに～ても-&gt;无论如何…也…</t>
+  </si>
+  <si>
+    <t>まさに</t>
+  </si>
+  <si>
+    <t>正是…</t>
+  </si>
+  <si>
+    <t>すっかり</t>
+  </si>
+  <si>
+    <t>完全，彻底</t>
+  </si>
+  <si>
+    <t>すなわち</t>
+  </si>
+  <si>
+    <t>也就是说，换言之</t>
+  </si>
+  <si>
+    <t>Vた + までだ</t>
+  </si>
+  <si>
+    <t>只是...罢了</t>
+  </si>
+  <si>
+    <t>したがって</t>
+  </si>
+  <si>
+    <t>因此</t>
+  </si>
+  <si>
+    <t>それに</t>
+  </si>
+  <si>
+    <t>而且，再加上</t>
+  </si>
+  <si>
+    <t>ようだ</t>
+  </si>
+  <si>
+    <t>好像...，似乎...</t>
+  </si>
+  <si>
+    <t>しかも</t>
+  </si>
+  <si>
+    <t>而且…；并且…</t>
+  </si>
+  <si>
+    <t>いったい</t>
+  </si>
+  <si>
+    <t>到底，究竟</t>
+  </si>
+  <si>
+    <t>二度と + 否定</t>
+  </si>
+  <si>
+    <t>再也（不）...</t>
+  </si>
+  <si>
+    <t>にどと + ひてい</t>
+  </si>
+  <si>
+    <t>かえって</t>
+  </si>
+  <si>
+    <t>反而，反倒</t>
+  </si>
+  <si>
+    <t>〜に限らず〜も</t>
+  </si>
+  <si>
+    <t>不仅...也...</t>
+  </si>
+  <si>
+    <t>〜にかぎらず〜も</t>
+  </si>
+  <si>
+    <t>〜なしには〜ない</t>
+  </si>
+  <si>
+    <t>如果没有...就不能...</t>
+  </si>
+  <si>
+    <t>〜おかげで</t>
+  </si>
+  <si>
+    <t>多亏了...</t>
+  </si>
+  <si>
+    <t>ようがない</t>
+  </si>
+  <si>
+    <t>没有办法做某事</t>
+  </si>
+  <si>
+    <t>よう-&gt;示例，像…一样</t>
+  </si>
+  <si>
+    <t>かれる</t>
+  </si>
+  <si>
+    <t>难以…</t>
+  </si>
+  <si>
+    <t>かれない-&gt;很可能(负面)</t>
+  </si>
+  <si>
+    <t>ようになる</t>
+  </si>
+  <si>
+    <t>(客观)变得能够...</t>
+  </si>
+  <si>
+    <t>ことになる-&gt;团体决定</t>
+  </si>
+  <si>
+    <t>如果…的话，大不了…</t>
+  </si>
+  <si>
+    <t>までだ</t>
+  </si>
+  <si>
+    <t>只能那样…</t>
+  </si>
+  <si>
+    <t>試合</t>
+  </si>
+  <si>
+    <t>比赛</t>
+  </si>
+  <si>
+    <t>しあい</t>
+  </si>
+  <si>
+    <t>放題</t>
+  </si>
+  <si>
+    <t>任意，随便（做某事）</t>
+  </si>
+  <si>
+    <t>ほうだい</t>
+  </si>
+  <si>
+    <t>とする</t>
+  </si>
+  <si>
+    <t>视作…</t>
+  </si>
+  <si>
+    <t>たことにする-&gt;当作…</t>
+  </si>
+  <si>
+    <t>ようにする</t>
+  </si>
+  <si>
+    <t>(主观)努力做到...</t>
+  </si>
+  <si>
+    <t>ことにする-&gt;主观决定</t>
+  </si>
+  <si>
+    <t>ほかない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只好...，只有…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同“しかなう”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まさか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)接否定，想不到会…(2)推测，该不会是…(3)单独使用，怎么会呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起こす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叫醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いつまでも</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一直…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うがい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗽口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なくなる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变得不再…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ようにする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚持…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拝見</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ご覧になる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「见る」尊他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>どれだけ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何种程度;多少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>どれだけ〜か</t>
-  </si>
-  <si>
-    <t>多么...啊</t>
-  </si>
-  <si>
-    <t>なんて～だろう-&gt;(感叹)多么…的啊</t>
-  </si>
-  <si>
-    <t>どうしても</t>
-  </si>
-  <si>
-    <t>(1)接否定，无论…也不…(2)务必</t>
-  </si>
-  <si>
-    <t>どんなに～ても-&gt;无论如何…也…</t>
-  </si>
-  <si>
-    <t>まさに</t>
-  </si>
-  <si>
-    <t>正是…</t>
-  </si>
-  <si>
-    <t>すっかり</t>
-  </si>
-  <si>
-    <t>完全，彻底</t>
-  </si>
-  <si>
-    <t>すなわち</t>
-  </si>
-  <si>
-    <t>也就是说，换言之</t>
-  </si>
-  <si>
-    <t>Vた + までだ</t>
-  </si>
-  <si>
-    <t>只是...罢了</t>
-  </si>
-  <si>
-    <t>したがって</t>
-  </si>
-  <si>
-    <t>因此</t>
-  </si>
-  <si>
-    <t>それに</t>
-  </si>
-  <si>
-    <t>而且，再加上</t>
-  </si>
-  <si>
-    <t>ようだ</t>
-  </si>
-  <si>
-    <t>好像...，似乎...</t>
-  </si>
-  <si>
-    <t>しかも</t>
-  </si>
-  <si>
-    <t>而且…；并且…</t>
-  </si>
-  <si>
-    <t>まさか</t>
-  </si>
-  <si>
-    <t>难道，怎会</t>
-  </si>
-  <si>
-    <t>いったい</t>
-  </si>
-  <si>
-    <t>到底，究竟</t>
-  </si>
-  <si>
-    <t>二度と + 否定</t>
-  </si>
-  <si>
-    <t>再也（不）...</t>
-  </si>
-  <si>
-    <t>にどと + ひてい</t>
-  </si>
-  <si>
-    <t>かえって</t>
-  </si>
-  <si>
-    <t>反而，反倒</t>
-  </si>
-  <si>
-    <t>〜に限らず〜も</t>
-  </si>
-  <si>
-    <t>不仅...也...</t>
-  </si>
-  <si>
-    <t>〜にかぎらず〜も</t>
-  </si>
-  <si>
-    <t>〜なしには〜ない</t>
-  </si>
-  <si>
-    <t>如果没有...就不能...</t>
-  </si>
-  <si>
-    <t>〜おかげで</t>
-  </si>
-  <si>
-    <t>多亏了...</t>
-  </si>
-  <si>
-    <t>ようがない</t>
-  </si>
-  <si>
-    <t>没有办法做某事</t>
-  </si>
-  <si>
-    <t>よう-&gt;示例，像…一样</t>
-  </si>
-  <si>
-    <t>ほかない</t>
-  </si>
-  <si>
-    <t>只好...，只有...</t>
-  </si>
-  <si>
-    <t>同“しかなう”</t>
-  </si>
-  <si>
-    <t>かれる</t>
-  </si>
-  <si>
-    <t>难以…</t>
-  </si>
-  <si>
-    <t>かれない-&gt;很可能(负面)</t>
-  </si>
-  <si>
-    <t>ようになる</t>
-  </si>
-  <si>
-    <t>(客观)变得能够...</t>
-  </si>
-  <si>
-    <t>ことになる-&gt;团体决定</t>
-  </si>
-  <si>
-    <t>～なら・ば・たら～Ｖるまで</t>
-  </si>
-  <si>
-    <t>如果…的话，大不了…</t>
-  </si>
-  <si>
-    <t>までだ</t>
-  </si>
-  <si>
-    <t>只能那样…</t>
-  </si>
-  <si>
-    <t>試合</t>
-  </si>
-  <si>
-    <t>比赛</t>
-  </si>
-  <si>
-    <t>しあい</t>
-  </si>
-  <si>
-    <t>放題</t>
-  </si>
-  <si>
-    <t>任意，随便（做某事）</t>
-  </si>
-  <si>
-    <t>ほうだい</t>
-  </si>
-  <si>
-    <t>とする</t>
-  </si>
-  <si>
-    <t>视作…</t>
-  </si>
-  <si>
-    <t>たことにする-&gt;当作…</t>
-  </si>
-  <si>
-    <t>ようにする</t>
-  </si>
-  <si>
-    <t>(主观)努力做到...</t>
-  </si>
-  <si>
-    <t>ことにする-&gt;主观决定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～なら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ば</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>たら～Ｖるまで</t>
+    </r>
+  </si>
+  <si>
+    <t>「见る」「読む」自谦语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,13 +406,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -340,11 +471,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -647,13 +779,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="3" max="3" width="30.375" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
@@ -674,412 +807,500 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9">
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12">
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
         <v>1</v>
       </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13">
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15">
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18">
+      <c r="C19" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
         <v>1</v>
       </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D20" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21">
+      <c r="C22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
         <v>1</v>
       </c>
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D22" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23">
+      <c r="C24" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
         <v>1</v>
       </c>
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B25" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24">
-        <v>0</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E25" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
         <v>1</v>
       </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26">
-        <v>0</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27">
-        <v>0</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28">
-        <v>0</v>
-      </c>
-      <c r="B28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29">
-        <v>0</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30">
-        <v>0</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31">
-        <v>0</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C33" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C31" t="s">
+      <c r="E33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32">
-        <v>0</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="C34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E34" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34">
-        <v>0</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>2</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E34" t="s">
+      <c r="C35" s="2" t="s">
         <v>84</v>
       </c>
     </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>2</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>2</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="2">
+        <v>2</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>2</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1090,7 +1311,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1100,7 +1321,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GRAMMAR/4_21_12.xlsx
+++ b/GRAMMAR/4_21_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -462,10 +462,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -479,10 +484,15 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -496,10 +506,15 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -517,10 +532,15 @@
           <t>なんて～だろう-&gt;(感叹)多么…的啊</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -536,6 +556,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>したがう-&gt;遵守;按照</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -555,10 +580,15 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -572,10 +602,15 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -589,6 +624,11 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -606,6 +646,11 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -627,6 +672,11 @@
           <t>どんなに～ても-&gt;无论如何…也…</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -644,10 +694,15 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -661,6 +716,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -682,6 +742,11 @@
           <t>ことにする-&gt;主观决定</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -699,6 +764,11 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -716,6 +786,11 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -733,6 +808,11 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -750,6 +830,11 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -771,6 +856,11 @@
           <t>たことにする-&gt;当作…</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -788,6 +878,11 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -805,6 +900,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -826,6 +926,11 @@
           <t>Vようとしたら-&gt;正想…时</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -843,10 +948,15 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -860,6 +970,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -877,6 +992,11 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -894,10 +1014,15 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -911,6 +1036,11 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -928,6 +1058,11 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -949,10 +1084,15 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -966,6 +1106,11 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -987,6 +1132,11 @@
           <t>Ｖる+つもり-&gt;准备做某事</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1008,6 +1158,11 @@
           <t>よう-&gt;示例，像…一样</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1025,6 +1180,11 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1046,6 +1206,11 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1067,6 +1232,11 @@
           <t>ことになる-&gt;团体决定</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1088,6 +1258,11 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1105,6 +1280,11 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1126,6 +1306,11 @@
           <t>かれない-&gt;很可能(负面)</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1147,6 +1332,11 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1164,6 +1354,11 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1181,6 +1376,11 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1200,6 +1400,11 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>同“しかなう”</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
